--- a/MA2026-projeto-pratico/MA2026-entrega-parcial/01-excel/agency.xlsx
+++ b/MA2026-projeto-pratico/MA2026-entrega-parcial/01-excel/agency.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\fatecsp-MA20262-equipe-07-colossenses\MA2026-projeto-pratico\MA2026-entrega-parcial\01-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5A07C0-DC63-4072-8008-CD403EEA7D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49775C4-C3A2-43A1-BB7B-C2EC157432F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{12D3D39E-1A24-42DA-8AD9-482000C10E20}"/>
   </bookViews>
@@ -81,14 +81,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -96,16 +88,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor theme="6" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -113,21 +125,290 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.59999389629810485"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.59999389629810485"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thick">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.59999389629810485"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thick">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.59999389629810485"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thick">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.59999389629810485"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thick">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6" tint="0.59999389629810485"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thick">
+          <color theme="0"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -138,6 +419,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B5E13A44-292B-427F-ABF8-29399769AEB5}" name="Agency" displayName="Agency" ref="A1:E2" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:E2" xr:uid="{B5E13A44-292B-427F-ABF8-29399769AEB5}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{133C4D6E-E748-4C98-857D-8C511C6ED666}" name="agency_id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{77EA78B4-2151-4342-9A5F-9A7E1E148963}" name="agency_name" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{237C36B2-A802-4FEF-96D0-D740269F654B}" name="agency_url" dataDxfId="4" dataCellStyle="Hiperlink"/>
+    <tableColumn id="4" xr3:uid="{653E0EC4-AA6D-4BD7-B81D-E19773CA3852}" name="agency_timezone" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{CDE33F92-30E6-463D-93D4-9EA7304B0995}" name="agency_lang" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -460,15 +755,15 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="3" width="40.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -484,20 +779,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -506,5 +801,8 @@
     <hyperlink ref="C2" r:id="rId1" xr:uid="{32EBA6BC-7EEB-4B5A-BF6C-86DFC28BD413}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>